--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS05_split_half_module_ledger.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS05_split_half_module_ledger.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 by manuscript/_h/build_supplementary_data.py</t>
+          <t>2026-10-04 by manuscript/_h/build_supplementary_data.py</t>
         </is>
       </c>
     </row>
